--- a/pdf2img/hasil_ekstraksi/table_4/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_4/tabel_1.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_extraction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cleaned_output" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,15 +30,21 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +58,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,306 +452,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>LAPORAN TRANSAKSI SPOT DAN DERIVATIF Per 31 Desembcr 202s</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TRANSAKSI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nilai Notional</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tujuan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tujuan</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tagihan dan Liabilitas Derivatit</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tagihan dan Liabilitas Derivatit</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 1 Spox</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Terkait dengan Nila! Tukar</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nilai Notional</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Trading</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hedging</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tagihan</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Liabilitas</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2 3 4 5 6</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Forwmd Option a Jual D Bol Hauu Swap</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B. 1 2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Larnya Terkalnt dengan Suku Bunga forward</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Opton 4 Jua</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>D Bel</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FuAure</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swap</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>专</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>arnya</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JUMLAH</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
